--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R542f27276c1948cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R731fa76fee1f445c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -471,34 +471,26 @@
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="14" t="str">
-        <x:v>失败收口</x:v>
+        <x:v>完成条件</x:v>
       </x:c>
       <x:c r="B15" s="21" t="str">
-        <x:v>tools/run-task.mjs调用Playwright；任一测试失败时清理本轮reports、evidence、test-results和临时运行目录，避免旧结果被误用</x:v>
+        <x:v>npm run test:e2e使用锁定版本的Playwright与Chromium完成所有场景，四份报表与逐场景证据相互对应</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="52" customHeight="1">
       <x:c r="A16" s="14" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>工作要点</x:v>
       </x:c>
       <x:c r="B16" s="21" t="str">
-        <x:v>npm run test:e2e可以在Windows11原生环境中使用锁定版本的Playwright与Chromium完成回归，四份报表与十二份证据相互对应，同一输入重复运行的结构化语义一致</x:v>
+        <x:v>读取三类业务输入；稳定定位；route响应序列；支付方式交互；最终请求参数；浏览器时间；焦点断言；trace与截图可用性</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="52" customHeight="1">
       <x:c r="A17" s="14" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>评分边界</x:v>
       </x:c>
       <x:c r="B17" s="21" t="str">
-        <x:v>真实Chromium进程；三类输入读取；稳定定位；route响应序列；支付方式交互；最终请求参数；浏览器时间；焦点断言；trace与截图可用性；失败清理</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="52" customHeight="1">
-      <x:c r="A18" s="14" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
-      </x:c>
-      <x:c r="B18" s="21" t="str">
-        <x:v>代码缩进、注释数量、内部函数名、测试标题措辞、CSV行顺序、JSON键顺序、trace与截图字节哈希及不改变业务结果的附加说明文件</x:v>
+        <x:v>代码缩进、注释数量、内部函数名、测试标题措辞、CSV行顺序、JSON键顺序及不改变业务结果的附加说明文件不计分</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R731fa76fee1f445c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Red2bda9398464525"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -394,20 +394,20 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="21" t="str">
-        <x:v>脱敏的订阅结账页、产品场景表、报价fixture、浏览器策略和故障测试</x:v>
+        <x:v>本次订阅结账回归批次的本地页面、产品场景表、报价响应和浏览器策略，客户字段已脱敏</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" s="14" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B6" s="21" t="str">
-        <x:v>解压输入数据包后，从input_data/app读取本地页面，从input_data/cases读取场景CSV，从input_data/fixtures读取报价响应，从input_data/policy读取浏览器策略，从input_data/starter读取故障配置与测试</x:v>
+        <x:v>建立稳定的结账页回归，让产品负责人查看场景结果，接口负责人核对报价请求，质量团队可通过trace和截图追查交互细节</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" s="14" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>输入文件</x:v>
       </x:c>
       <x:c r="B7" s="21" t="str">
         <x:v>app/checkout.html；app/checkout.js；app/styles.css；cases/subscription_checkout_cases.csv；fixtures/quote_responses.json；policy/test_contract.json；starter/playwright.config.mjs；starter/tests/subscription_checkout.spec.mjs；package.json；package-lock.json</x:v>
@@ -415,84 +415,77 @@
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" s="14" t="str">
-        <x:v>目标输出文件</x:v>
+        <x:v>交付文件</x:v>
       </x:c>
       <x:c r="B8" s="21" t="str">
-        <x:v>output/playwright.config.mjs；output/tests/subscription_checkout.spec.mjs；output/reports/case_results.csv；output/reports/network_contract.csv；output/reports/evidence_manifest.csv；output/reports/run_summary.json；output/evidence/traces中的场景ZIP；output/evidence/screenshots中的场景PNG</x:v>
+        <x:v>output/playwright.config.mjs；output/tests/subscription_checkout.spec.mjs；output/reports/case_results.csv；output/reports/network_contract.csv；output/reports/evidence_manifest.csv；output/reports/run_summary.json；output/evidence/traces下的场景ZIP；output/evidence/screenshots下的场景PNG</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" s="14" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>场景流程</x:v>
       </x:c>
       <x:c r="B9" s="21" t="str">
-        <x:v>使用Playwright读取三类业务输入，启动本机结账页，按deep_link进入场景并选择支付方式，拦截报价请求，核对页面状态、最终查询参数、浏览器时间与焦点，再写出四份报表和逐场景证据</x:v>
+        <x:v>按deep_link进入结账页，根据场景选择支付方式，读取套餐、席位、地区、优惠码、学生年龄、状态提示、总价和继续按钮状态</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="14" t="str">
-        <x:v>浏览器配置</x:v>
+        <x:v>报价请求</x:v>
       </x:c>
       <x:c r="B10" s="21" t="str">
-        <x:v>只使用Chromium；Playwright配置启动127.0.0.1上的静态webServer，单worker串行运行，临时产物留在当前任务目录；正式测试不访问外部服务</x:v>
+        <x:v>使用test_contract.json中的route模式接管报价请求，按quote_responses.json返回状态与正文，并记录最终plan、seats、region、coupon和payment</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="14" t="str">
-        <x:v>报价拦截</x:v>
+        <x:v>Playwright配置</x:v>
       </x:c>
       <x:c r="B11" s="21" t="str">
-        <x:v>route模式来自test_contract.json，响应状态与正文来自quote_responses.json；记录每次拦截状态，最终plan、seats、region、coupon和payment必须与场景一致</x:v>
+        <x:v>使用Chromium和本机静态webServer，按test_contract.json设置浏览器时间与视口，报价请求只读取本地fixture</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="14" t="str">
-        <x:v>页面定位</x:v>
+        <x:v>页面交互</x:v>
       </x:c>
       <x:c r="B12" s="21" t="str">
-        <x:v>套餐、状态和总价使用test id，地区、优惠码和学生年龄使用label，支付方式与继续按钮使用role和可访问名称；核心操作不依赖nth或元素位置</x:v>
+        <x:v>使用role、label或test id定位核心控件，通过页面操作切换支付方式，同时检查套餐、地区、支付方式和可用继续按钮的键盘焦点</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="14" t="str">
-        <x:v>时间与焦点</x:v>
+        <x:v>页面记录</x:v>
       </x:c>
       <x:c r="B13" s="21" t="str">
-        <x:v>page.clock使用fixed_browser_time，浏览器内Date结果写入case_results.csv；套餐、地区和支付方式都要检查焦点，可用的继续按钮也要检查</x:v>
+        <x:v>每个case_id保存一份trace ZIP和一张完整页面PNG，evidence_manifest.csv使用相对output的路径关联场景、状态和页面提示</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="14" t="str">
-        <x:v>执行证据</x:v>
+        <x:v>报表交接</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>每个case_id保存一份可打开的trace ZIP和一张完整页面PNG，evidence_manifest.csv记录相对output根目录的证据路径、最终状态和页面提示</x:v>
+        <x:v>case_results.csv记录页面结果，network_contract.csv记录报价过程，evidence_manifest.csv索引页面记录，run_summary.json汇总本次发布回归</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="14" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>运行入口</x:v>
       </x:c>
       <x:c r="B15" s="21" t="str">
-        <x:v>npm run test:e2e使用锁定版本的Playwright与Chromium完成所有场景，四份报表与逐场景证据相互对应</x:v>
+        <x:v>在input_data目录执行npm run test:e2e，由package.json调用Playwright测试并把交付物写入output</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="52" customHeight="1">
       <x:c r="A16" s="14" t="str">
-        <x:v>工作要点</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B16" s="21" t="str">
-        <x:v>读取三类业务输入；稳定定位；route响应序列；支付方式交互；最终请求参数；浏览器时间；焦点断言；trace与截图可用性</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="52" customHeight="1">
-      <x:c r="A17" s="14" t="str">
-        <x:v>评分边界</x:v>
-      </x:c>
-      <x:c r="B17" s="21" t="str">
-        <x:v>代码缩进、注释数量、内部函数名、测试标题措辞、CSV行顺序、JSON键顺序及不改变业务结果的附加说明文件不计分</x:v>
-      </x:c>
-    </x:row>
+        <x:v>可以拆分辅助模块或调整报表行顺序；必须通过Chromium交互读取页面结果，不能用静态报表代替页面操作</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="52" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
